--- a/RAMON FRANCO/Septiembre/CALCULO EDESUR RAMON FRANCO Septiembre.xlsx
+++ b/RAMON FRANCO/Septiembre/CALCULO EDESUR RAMON FRANCO Septiembre.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CC8ACB-95C9-4511-94CE-2ED98BD4CFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47608162-39A8-48C0-9FD8-602DAC9936AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -339,7 +339,7 @@
     <t>QUIENES ADEUDEN DOS MESES DE EDESUR SERAN DESCONECTADOS DE LA RED. SALUDOS CORDIALES.</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 15/09</t>
+    <t>EDESUR - VENCIMIENTO 15/10</t>
   </si>
 </sst>
 </file>
@@ -347,13 +347,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="167" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -751,7 +751,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="4" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="103">
@@ -764,13 +764,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -778,35 +778,35 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -822,30 +822,30 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="6" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -864,34 +864,54 @@
     <xf numFmtId="43" fontId="5" fillId="6" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -904,26 +924,6 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1232,12 +1232,12 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" hidden="1" customWidth="1"/>
     <col min="6" max="7" width="10.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="13" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="7.140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="15.42578125" customWidth="1"/>
@@ -1250,22 +1250,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="88"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="100"/>
       <c r="O1" s="48"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3"/>
@@ -1419,17 +1419,17 @@
         <v>8</v>
       </c>
       <c r="C8" s="84">
-        <v>1297943.02</v>
+        <v>1328569.67</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="10"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="93">
+      <c r="J8" s="86"/>
+      <c r="K8" s="87">
         <f>C8-J32</f>
-        <v>872391.07259</v>
+        <v>805907.95712000038</v>
       </c>
       <c r="L8" s="47"/>
       <c r="M8" s="10"/>
@@ -1465,10 +1465,10 @@
       <c r="I9" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="96" t="s">
+      <c r="J9" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="96" t="s">
+      <c r="K9" s="90" t="s">
         <v>94</v>
       </c>
       <c r="L9" s="44" t="s">
@@ -1485,7 +1485,7 @@
       <c r="A10" s="59">
         <v>1</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="95">
         <v>1</v>
       </c>
       <c r="C10" s="71" t="s">
@@ -1497,11 +1497,11 @@
       <c r="E10" s="73">
         <v>7.99</v>
       </c>
-      <c r="F10" s="102">
+      <c r="F10" s="96">
         <f>+E10</f>
         <v>7.99</v>
       </c>
-      <c r="G10" s="102">
+      <c r="G10" s="96">
         <f>+F10</f>
         <v>7.99</v>
       </c>
@@ -1512,13 +1512,13 @@
         <f t="shared" ref="I10:I32" si="0">H10*7%</f>
         <v>0</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="93">
         <f>M10*93.787</f>
         <v>0</v>
       </c>
-      <c r="K10" s="99">
+      <c r="K10" s="93">
         <f>K8*E10%</f>
-        <v>69704.046699940998</v>
+        <v>64392.045773888029</v>
       </c>
       <c r="L10" s="76"/>
       <c r="M10" s="77">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="N10" s="78">
         <f>J10+K10+L10</f>
-        <v>69704.046699940998</v>
+        <v>64392.045773888029</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1546,12 +1546,11 @@
       <c r="E11" s="53">
         <v>6.05</v>
       </c>
-      <c r="F11" s="100">
-        <f>E11+200</f>
-        <v>206.05</v>
-      </c>
-      <c r="G11" s="100">
+      <c r="F11" s="94">
         <v>490.1</v>
+      </c>
+      <c r="G11" s="94">
+        <v>492.1</v>
       </c>
       <c r="H11" s="54">
         <v>0</v>
@@ -1560,22 +1559,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="97">
-        <f t="shared" ref="J11:J27" si="1">M11*93.787</f>
-        <v>26640.197350000002</v>
-      </c>
-      <c r="K11" s="97">
+      <c r="J11" s="91">
+        <f>M11*173.944</f>
+        <v>347.88799999999998</v>
+      </c>
+      <c r="K11" s="91">
         <f>K8*E11%</f>
-        <v>52779.659891694995</v>
+        <v>48757.43140576002</v>
       </c>
       <c r="L11" s="56"/>
       <c r="M11" s="57">
-        <f t="shared" ref="M11:M31" si="2">G11-F11</f>
-        <v>284.05</v>
+        <f t="shared" ref="M11:M31" si="1">G11-F11</f>
+        <v>2</v>
       </c>
       <c r="N11" s="69">
-        <f t="shared" ref="N11:N31" si="3">J11+K11+L11</f>
-        <v>79419.85724169499</v>
+        <f t="shared" ref="N11:N31" si="2">J11+K11+L11</f>
+        <v>49105.319405760019</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1594,11 +1593,11 @@
       <c r="E12" s="53">
         <v>6.02</v>
       </c>
-      <c r="F12" s="100">
-        <v>4519.8999999999996</v>
-      </c>
-      <c r="G12" s="100">
+      <c r="F12" s="94">
         <v>4880.8999999999996</v>
+      </c>
+      <c r="G12" s="94">
+        <v>5125.8999999999996</v>
       </c>
       <c r="H12" s="54">
         <v>0</v>
@@ -1607,22 +1606,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="97">
-        <f t="shared" si="1"/>
-        <v>33857.107000000004</v>
-      </c>
-      <c r="K12" s="97">
+      <c r="J12" s="91">
+        <f t="shared" ref="J12:J21" si="3">M12*173.944</f>
+        <v>42616.28</v>
+      </c>
+      <c r="K12" s="91">
         <f>K8*E12%</f>
-        <v>52517.942569917999</v>
+        <v>48515.659018624021</v>
       </c>
       <c r="L12" s="56"/>
       <c r="M12" s="57">
         <f>G12-F12</f>
-        <v>361</v>
+        <v>245</v>
       </c>
       <c r="N12" s="69">
-        <f t="shared" si="3"/>
-        <v>86375.049569918003</v>
+        <f t="shared" si="2"/>
+        <v>91131.93901862402</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1641,37 +1640,37 @@
       <c r="E13" s="64">
         <v>7.63</v>
       </c>
-      <c r="F13" s="100">
+      <c r="F13" s="94">
         <f>E13+250</f>
         <v>257.63</v>
       </c>
-      <c r="G13" s="100">
+      <c r="G13" s="94">
         <f>F13+250</f>
         <v>507.63</v>
       </c>
       <c r="H13" s="65">
         <v>0</v>
       </c>
-      <c r="I13" s="91">
+      <c r="I13" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="97">
-        <f t="shared" si="1"/>
-        <v>23446.75</v>
-      </c>
-      <c r="K13" s="98">
+      <c r="J13" s="91">
+        <f t="shared" si="3"/>
+        <v>43486</v>
+      </c>
+      <c r="K13" s="92">
         <f>K8*E13%</f>
-        <v>66563.438838616989</v>
+        <v>61490.777128256021</v>
       </c>
       <c r="L13" s="56"/>
       <c r="M13" s="66">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="N13" s="69">
         <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="N13" s="69">
-        <f t="shared" si="3"/>
-        <v>90010.188838616989</v>
+        <v>104976.77712825601</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -1690,11 +1689,11 @@
       <c r="E14" s="53">
         <v>6.05</v>
       </c>
-      <c r="F14" s="100">
+      <c r="F14" s="94">
         <f>+E14+250</f>
         <v>256.05</v>
       </c>
-      <c r="G14" s="100">
+      <c r="G14" s="94">
         <f>+F14+250</f>
         <v>506.05</v>
       </c>
@@ -1705,22 +1704,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="97">
-        <f t="shared" si="1"/>
-        <v>23446.75</v>
-      </c>
-      <c r="K14" s="97">
+      <c r="J14" s="91">
+        <f t="shared" si="3"/>
+        <v>43486</v>
+      </c>
+      <c r="K14" s="91">
         <f>K8*E14%</f>
-        <v>52779.659891694995</v>
+        <v>48757.43140576002</v>
       </c>
       <c r="L14" s="56"/>
       <c r="M14" s="57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>250</v>
       </c>
       <c r="N14" s="69">
         <f>J14+K14+L14</f>
-        <v>76226.409891694988</v>
+        <v>92243.431405760028</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -1739,11 +1738,11 @@
       <c r="E15" s="53">
         <v>6.02</v>
       </c>
-      <c r="F15" s="100">
-        <v>4914.8999999999996</v>
-      </c>
-      <c r="G15" s="100">
+      <c r="F15" s="94">
         <v>5019.8</v>
+      </c>
+      <c r="G15" s="94">
+        <v>5182.8999999999996</v>
       </c>
       <c r="H15" s="54">
         <v>0</v>
@@ -1752,22 +1751,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="97">
-        <f t="shared" si="1"/>
-        <v>9838.2563000000519</v>
-      </c>
-      <c r="K15" s="97">
+      <c r="J15" s="91">
+        <f t="shared" si="3"/>
+        <v>28370.266399999902</v>
+      </c>
+      <c r="K15" s="91">
         <f>K8*E15%</f>
-        <v>52517.942569917999</v>
+        <v>48515.659018624021</v>
       </c>
       <c r="L15" s="56"/>
       <c r="M15" s="57">
+        <f t="shared" si="1"/>
+        <v>163.09999999999945</v>
+      </c>
+      <c r="N15" s="69">
         <f t="shared" si="2"/>
-        <v>104.90000000000055</v>
-      </c>
-      <c r="N15" s="69">
-        <f t="shared" si="3"/>
-        <v>62356.198869918051</v>
+        <v>76885.925418623927</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -1786,11 +1785,11 @@
       <c r="E16" s="53">
         <v>7.63</v>
       </c>
-      <c r="F16" s="100">
-        <v>14488.2</v>
-      </c>
-      <c r="G16" s="100">
+      <c r="F16" s="94">
         <v>14922.1</v>
+      </c>
+      <c r="G16" s="94">
+        <v>15267.9</v>
       </c>
       <c r="H16" s="26">
         <v>0</v>
@@ -1799,22 +1798,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="97">
-        <f t="shared" si="1"/>
-        <v>40694.179299999967</v>
-      </c>
-      <c r="K16" s="97">
+      <c r="J16" s="91">
+        <f t="shared" si="3"/>
+        <v>60149.83519999987</v>
+      </c>
+      <c r="K16" s="91">
         <f>K8*E16%</f>
-        <v>66563.438838616989</v>
+        <v>61490.777128256021</v>
       </c>
       <c r="L16" s="56"/>
       <c r="M16" s="57">
+        <f t="shared" si="1"/>
+        <v>345.79999999999927</v>
+      </c>
+      <c r="N16" s="69">
         <f t="shared" si="2"/>
-        <v>433.89999999999964</v>
-      </c>
-      <c r="N16" s="69">
-        <f t="shared" si="3"/>
-        <v>107257.61813861696</v>
+        <v>121640.6123282559</v>
       </c>
       <c r="P16" s="50"/>
     </row>
@@ -1834,11 +1833,11 @@
       <c r="E17" s="53">
         <v>6.05</v>
       </c>
-      <c r="F17" s="100">
-        <v>10498.59</v>
-      </c>
-      <c r="G17" s="100">
+      <c r="F17" s="94">
         <v>10499.21</v>
+      </c>
+      <c r="G17" s="94">
+        <v>10827.14</v>
       </c>
       <c r="H17" s="54">
         <v>0</v>
@@ -1847,22 +1846,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="97">
-        <f t="shared" si="1"/>
-        <v>58.147939999904466</v>
-      </c>
-      <c r="K17" s="97">
+      <c r="J17" s="91">
+        <f t="shared" si="3"/>
+        <v>57041.455920000044</v>
+      </c>
+      <c r="K17" s="91">
         <f>K8*E17%</f>
-        <v>52779.659891694995</v>
+        <v>48757.43140576002</v>
       </c>
       <c r="L17" s="56"/>
       <c r="M17" s="57">
+        <f t="shared" si="1"/>
+        <v>327.93000000000029</v>
+      </c>
+      <c r="N17" s="69">
         <f t="shared" si="2"/>
-        <v>0.61999999999898137</v>
-      </c>
-      <c r="N17" s="69">
-        <f t="shared" si="3"/>
-        <v>52837.807831694903</v>
+        <v>105798.88732576006</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1881,11 +1880,12 @@
       <c r="E18" s="53">
         <v>6.02</v>
       </c>
-      <c r="F18" s="100">
-        <v>8344.6</v>
-      </c>
-      <c r="G18" s="100">
+      <c r="F18" s="94">
         <v>8492.7999999999993</v>
+      </c>
+      <c r="G18" s="94">
+        <f>F18+150</f>
+        <v>8642.7999999999993</v>
       </c>
       <c r="H18" s="54">
         <v>0</v>
@@ -1894,22 +1894,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="97">
-        <f t="shared" si="1"/>
-        <v>13899.233399999899</v>
-      </c>
-      <c r="K18" s="97">
+      <c r="J18" s="91">
+        <f t="shared" si="3"/>
+        <v>26091.599999999999</v>
+      </c>
+      <c r="K18" s="91">
         <f>K8*E18%</f>
-        <v>52517.942569917999</v>
+        <v>48515.659018624021</v>
       </c>
       <c r="L18" s="56"/>
       <c r="M18" s="57">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="N18" s="69">
         <f t="shared" si="2"/>
-        <v>148.19999999999891</v>
-      </c>
-      <c r="N18" s="69">
-        <f t="shared" si="3"/>
-        <v>66417.175969917895</v>
+        <v>74607.259018624027</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1928,11 +1928,11 @@
       <c r="E19" s="67">
         <v>21.2</v>
       </c>
-      <c r="F19" s="100">
-        <v>22661.67</v>
-      </c>
-      <c r="G19" s="100">
+      <c r="F19" s="94">
         <v>23124.77</v>
+      </c>
+      <c r="G19" s="94">
+        <v>23463.64</v>
       </c>
       <c r="H19" s="26">
         <v>0</v>
@@ -1941,22 +1941,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="97">
-        <f t="shared" si="1"/>
-        <v>43432.759700000206</v>
-      </c>
-      <c r="K19" s="97">
+      <c r="J19" s="91">
+        <f t="shared" si="3"/>
+        <v>58944.403279999817</v>
+      </c>
+      <c r="K19" s="91">
         <f>K8*E19%</f>
-        <v>184946.90738908001</v>
+        <v>170852.48690944008</v>
       </c>
       <c r="L19" s="56"/>
       <c r="M19" s="57">
         <f>G19-F19</f>
-        <v>463.10000000000218</v>
+        <v>338.86999999999898</v>
       </c>
       <c r="N19" s="69">
-        <f t="shared" si="3"/>
-        <v>228379.66708908021</v>
+        <f t="shared" si="2"/>
+        <v>229796.8901894399</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1975,13 +1975,13 @@
       <c r="E20" s="53">
         <v>6.81</v>
       </c>
-      <c r="F20" s="100">
-        <f>E20+480</f>
-        <v>486.81</v>
-      </c>
-      <c r="G20" s="100">
+      <c r="F20" s="94">
+        <f>E20+600</f>
+        <v>606.80999999999995</v>
+      </c>
+      <c r="G20" s="94">
         <f>F20+600</f>
-        <v>1086.81</v>
+        <v>1206.81</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -1990,22 +1990,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="97">
-        <f t="shared" si="1"/>
-        <v>56272.200000000004</v>
-      </c>
-      <c r="K20" s="97">
+      <c r="J20" s="91">
+        <f t="shared" si="3"/>
+        <v>104366.39999999999</v>
+      </c>
+      <c r="K20" s="91">
         <f>K8*E20%</f>
-        <v>59409.832043378992</v>
+        <v>54882.331879872021</v>
       </c>
       <c r="L20" s="56"/>
       <c r="M20" s="57">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="N20" s="69">
         <f t="shared" si="2"/>
-        <v>600</v>
-      </c>
-      <c r="N20" s="69">
-        <f t="shared" si="3"/>
-        <v>115682.032043379</v>
+        <v>159248.73187987201</v>
       </c>
       <c r="P20" s="33"/>
     </row>
@@ -2025,11 +2025,11 @@
       <c r="E21" s="53">
         <v>6.52</v>
       </c>
-      <c r="F21" s="100">
-        <v>13266.27</v>
-      </c>
-      <c r="G21" s="100">
+      <c r="F21" s="94">
         <v>14907.93</v>
+      </c>
+      <c r="G21" s="94">
+        <v>15240</v>
       </c>
       <c r="H21" s="26">
         <v>0</v>
@@ -2038,22 +2038,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="97">
-        <f t="shared" si="1"/>
-        <v>153966.36642000001</v>
-      </c>
-      <c r="K21" s="97">
+      <c r="J21" s="91">
+        <f t="shared" si="3"/>
+        <v>57761.584079999942</v>
+      </c>
+      <c r="K21" s="91">
         <f>K8*E21%</f>
-        <v>56879.897932867992</v>
+        <v>52545.198804224019</v>
       </c>
       <c r="L21" s="56"/>
       <c r="M21" s="57">
+        <f t="shared" si="1"/>
+        <v>332.06999999999971</v>
+      </c>
+      <c r="N21" s="69">
         <f t="shared" si="2"/>
-        <v>1641.6599999999999</v>
-      </c>
-      <c r="N21" s="69">
-        <f t="shared" si="3"/>
-        <v>210846.26435286799</v>
+        <v>110306.78288422397</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2085,22 +2085,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="99">
+      <c r="J22" s="93">
+        <f t="shared" ref="J11:J27" si="4">M22*93.787</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="93">
         <f>K8*E22%</f>
-        <v>10294.214656562001</v>
+        <v>9509.7138940160039</v>
       </c>
       <c r="L22" s="76"/>
       <c r="M22" s="77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="78">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="78">
-        <f t="shared" si="3"/>
-        <v>10294.214656562001</v>
+        <v>9509.7138940160039</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2132,22 +2132,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="99">
+      <c r="J23" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="93">
         <f>K8*E23%</f>
-        <v>10206.975549302999</v>
+        <v>9429.1230983040041</v>
       </c>
       <c r="L23" s="76"/>
       <c r="M23" s="77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="78">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="78">
-        <f t="shared" si="3"/>
-        <v>10206.975549302999</v>
+        <v>9429.1230983040041</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2179,22 +2179,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="97">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="97">
+      <c r="J24" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="91">
         <f>K8*E24%</f>
-        <v>9247.3453694540003</v>
+        <v>8542.6243454720043</v>
       </c>
       <c r="L24" s="56"/>
       <c r="M24" s="57">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="69">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="69">
-        <f t="shared" si="3"/>
-        <v>9247.3453694540003</v>
+        <v>8542.6243454720043</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2226,22 +2226,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="99">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="99">
+      <c r="J25" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="93">
         <f>K8*E25%</f>
-        <v>4449.1944702090004</v>
+        <v>4110.1305813120025</v>
       </c>
       <c r="L25" s="76"/>
       <c r="M25" s="82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="78">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="78">
-        <f t="shared" si="3"/>
-        <v>4449.1944702090004</v>
+        <v>4110.1305813120025</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2273,22 +2273,22 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="94">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="95">
+      <c r="J26" s="88">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="89">
         <f>K8*E26%</f>
-        <v>2355.455895993</v>
+        <v>2175.951484224001</v>
       </c>
       <c r="L26" s="45"/>
       <c r="M26" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="70">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="70">
-        <f t="shared" si="3"/>
-        <v>2355.455895993</v>
+        <v>2175.951484224001</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2321,21 +2321,21 @@
         <v>0</v>
       </c>
       <c r="J27" s="41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K27" s="45">
         <f>K8*E27%</f>
-        <v>15877.517521138001</v>
+        <v>14667.524819584009</v>
       </c>
       <c r="L27" s="45"/>
       <c r="M27" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="70">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N27" s="70">
-        <f t="shared" si="3"/>
-        <v>15877.517521138001</v>
+        <v>14667.524819584009</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2365,11 +2365,11 @@
       <c r="K28" s="45"/>
       <c r="L28" s="45"/>
       <c r="M28" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N28" s="19">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2400,11 +2400,11 @@
       <c r="K29" s="45"/>
       <c r="L29" s="45"/>
       <c r="M29" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="19">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2435,11 +2435,11 @@
       <c r="K30" s="45"/>
       <c r="L30" s="45"/>
       <c r="M30" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="19">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2470,11 +2470,11 @@
       <c r="K31" s="45"/>
       <c r="L31" s="45"/>
       <c r="M31" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="19">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="19">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G32" s="18">
         <f>SUM(G14:G31)+G13+G12+G11+G10</f>
-        <v>84446.090000000011</v>
+        <v>86470.86</v>
       </c>
       <c r="H32" s="19">
         <v>0</v>
@@ -2507,11 +2507,11 @@
       </c>
       <c r="J32" s="41">
         <f>J27+J26+J25+J24+J23+J22+J21+J20+J19+J18+J17+J16+J15+J14+J13+J12+J11+J10</f>
-        <v>425551.94741000002</v>
+        <v>522661.7128799996</v>
       </c>
       <c r="K32" s="45">
         <f>K27+K26+K25+K24+K23+K22+K21+K20+K18+K19+K17+K16+K15+K14+K13+K12+K11+K10</f>
-        <v>872391.07259</v>
+        <v>805907.95712000027</v>
       </c>
       <c r="L32" s="45">
         <f>SUM(L10:L31)</f>
@@ -2519,11 +2519,11 @@
       </c>
       <c r="M32" s="43">
         <f>SUM(M14:M31)+M12+M13+M11+M10</f>
-        <v>4537.43</v>
+        <v>3004.7699999999977</v>
       </c>
       <c r="N32" s="19">
         <f>N27+N26+N25+N24+N23+N22+N21+N20+N19+N18+N17+N16+N15+N14+N13++N12+N11+N10</f>
-        <v>1297943.02</v>
+        <v>1328569.6699999997</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="J33" s="30">
         <f>SUM(J10:J32)</f>
-        <v>851103.89482000005</v>
+        <v>1045323.4257599991</v>
       </c>
       <c r="K33" s="46"/>
       <c r="L33" s="46"/>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="N33" s="29">
         <f>SUM(N10:N32)</f>
-        <v>2595886.04</v>
+        <v>2657139.34</v>
       </c>
       <c r="O33" s="5"/>
       <c r="P33" s="2" t="e">
-        <f t="shared" ref="P33:P34" si="4">J33/C31*100</f>
+        <f t="shared" ref="P33:P34" si="5">J33/C31*100</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2565,23 +2565,23 @@
       <c r="A34" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="89" t="s">
+      <c r="C34" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="86"/>
-      <c r="H34" s="86"/>
-      <c r="I34" s="86"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="86"/>
-      <c r="N34" s="87"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="98"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="98"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="98"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="98"/>
+      <c r="N34" s="99"/>
       <c r="O34" s="31"/>
       <c r="P34" s="2" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2594,61 +2594,61 @@
       <c r="P35" s="2"/>
     </row>
     <row r="36" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="90" t="s">
+      <c r="C36" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
+      <c r="D36" s="102"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="102"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="102"/>
+      <c r="K36" s="102"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="102"/>
       <c r="P36" s="2"/>
     </row>
     <row r="37" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="90"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="90"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="90"/>
-      <c r="I37" s="90"/>
-      <c r="J37" s="90"/>
-      <c r="K37" s="90"/>
-      <c r="L37" s="90"/>
-      <c r="M37" s="90"/>
+      <c r="C37" s="102"/>
+      <c r="D37" s="102"/>
+      <c r="E37" s="102"/>
+      <c r="F37" s="102"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="102"/>
+      <c r="I37" s="102"/>
+      <c r="J37" s="102"/>
+      <c r="K37" s="102"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="102"/>
       <c r="P37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="90"/>
-      <c r="G38" s="90"/>
-      <c r="H38" s="90"/>
-      <c r="I38" s="90"/>
-      <c r="J38" s="90"/>
-      <c r="K38" s="90"/>
-      <c r="L38" s="90"/>
-      <c r="M38" s="90"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
       <c r="P38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="90"/>
-      <c r="D39" s="90"/>
-      <c r="E39" s="90"/>
-      <c r="F39" s="90"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="90"/>
-      <c r="I39" s="90"/>
-      <c r="J39" s="90"/>
-      <c r="K39" s="90"/>
-      <c r="L39" s="90"/>
-      <c r="M39" s="90"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="102"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
       <c r="P39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,21 +6528,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="88"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="100"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8134,19 +8134,19 @@
       <c r="A35" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="86"/>
-      <c r="H35" s="86"/>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="86"/>
-      <c r="M35" s="87"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="98"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="98"/>
+      <c r="H35" s="98"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="98"/>
+      <c r="K35" s="98"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="99"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>

--- a/RAMON FRANCO/Septiembre/CALCULO EDESUR RAMON FRANCO Septiembre.xlsx
+++ b/RAMON FRANCO/Septiembre/CALCULO EDESUR RAMON FRANCO Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47608162-39A8-48C0-9FD8-602DAC9936AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C2A079-659A-4B93-88E2-E5A330D9B013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1911,6 +1911,10 @@
         <f t="shared" si="2"/>
         <v>74607.259018624027</v>
       </c>
+      <c r="P18" s="33">
+        <f>N10+N22+N23+N24+N25+N14+N15+N11+N17+N20</f>
+        <v>579265.93312876811</v>
+      </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="59">
@@ -2086,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="93">
-        <f t="shared" ref="J11:J27" si="4">M22*93.787</f>
+        <f t="shared" ref="J22:J27" si="4">M22*93.787</f>
         <v>0</v>
       </c>
       <c r="K22" s="93">
